--- a/artfynd/A 57163-2025 artfynd.xlsx
+++ b/artfynd/A 57163-2025 artfynd.xlsx
@@ -675,42 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96585039</v>
+        <v>96585038</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>435460.2013813898</v>
+        <v>435460</v>
       </c>
       <c r="R2" t="n">
-        <v>6481158.231157207</v>
+        <v>6481158</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,19 +754,9 @@
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96585038</v>
+        <v>96585039</v>
       </c>
       <c r="B3" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,26 +800,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -855,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>435460.2013813898</v>
+        <v>435460</v>
       </c>
       <c r="R3" t="n">
-        <v>6481158.231157207</v>
+        <v>6481158</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -888,19 +868,9 @@
           <t>2021-10-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -936,12 +906,7 @@
         <v>104132114</v>
       </c>
       <c r="B4" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1058,7 +1023,7 @@
         <v>125796261</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1124,7 @@
         <v>125796263</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 57163-2025 artfynd.xlsx
+++ b/artfynd/A 57163-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96585038</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96585039</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104132114</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125796261</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,8 +1244,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125796263</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>